--- a/personal_trainer_forms/004_fitness_class_evaluation_form--personal_trainer_forms.xlsx
+++ b/personal_trainer_forms/004_fitness_class_evaluation_form--personal_trainer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>instructors</t>
+          <t>instructors_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>facilities_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>Facilities 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>exercise_selection</t>
+          <t>exercise_selection_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>exercise_selection</t>
+          <t>Exercise Selection 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>class_structure</t>
+          <t>class_structure_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>class_structure</t>
+          <t>Class Structure 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>equipment_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>Equipment 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>feedback_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Feedback 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>schedule</t>
+          <t>schedule_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>schedule</t>
+          <t>Schedule 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>instructors_choices</t>
+          <t>instructors_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1300,7 +1300,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>instructors_choices</t>
+          <t>instructors_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>facilities_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>facilities_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>exercise_selection_choices</t>
+          <t>exercise_selection_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>exercise_selection_choices</t>
+          <t>exercise_selection_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>class_structure_choices</t>
+          <t>class_structure_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1436,7 +1436,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>class_structure_choices</t>
+          <t>class_structure_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>equipment_choices</t>
+          <t>equipment_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>equipment_choices</t>
+          <t>equipment_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>feedback_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1504,7 +1504,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>feedback_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
